--- a/.claude/skills/controlm-runbook-automation-excel/controlm-runbook-template.xlsx
+++ b/.claude/skills/controlm-runbook-automation-excel/controlm-runbook-template.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>90123</t>
+          <t>70004</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PRDGRP-OHUB-90123-UPD-TRUST-UPD</t>
+          <t>PRDGRP-OHUB-70004-UPD-TRUST-UPD</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -697,7 +697,7 @@
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>/apps/etl/tenants/dpl_utils/dt-accelerators/dt-launcher-current.jar
-/apps/etl/tenants/ohub_data_warehouse/cfg/90123-epv-conf.json</t>
+/apps/etl/tenants/ohub_data_warehouse/cfg/70004-epv-conf.json</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -983,7 +983,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>90123</t>
+          <t>70004</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
@@ -1366,7 +1366,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PRDGRP-OHUB-90123-UPD-TRUST-UPD</t>
+          <t>PRDGRP-OHUB-70004-UPD-TRUST-UPD</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PRDGRP-OHUB-90123-UPD-TRUST-UPD</t>
+          <t>PRDGRP-OHUB-70004-UPD-TRUST-UPD</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1608,7 +1608,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PRDGRP-OHUB-90123-UPD-TRUST-UPD</t>
+          <t>PRDGRP-OHUB-70004-UPD-TRUST-UPD</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>prod_90123_db.ohub_svc_col_v</t>
+          <t>prod_70004_db.ohub_svc_col_v</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
